--- a/Press System Test Case Outputs.xlsx
+++ b/Press System Test Case Outputs.xlsx
@@ -1,40 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28129"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://purdue0-my.sharepoint.com/personal/tucke193_purdue_edu/Documents/PSP/Test Stand/PSPL_Test_Stand/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="30" documentId="11_2B59D9BF08C4D3A54CCDCDBECD328E9B5299384E" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A049798D-7BC2-4BE5-B716-1BEB38CAA83E}"/>
+  <xr:revisionPtr revIDLastSave="2" documentId="11_2B59D9BF4E64D59B50CCCD6AEDF5AFEF5299387C" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9867DC22-627A-426C-9CA7-D7FC61860CCB}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-93" yWindow="-93" windowWidth="25786" windowHeight="13866" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Test 0; Config 1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="223" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="207">
   <si>
     <t>T (K)</t>
   </si>
@@ -72,13 +59,13 @@
     <t>Tube, stations 2-3:</t>
   </si>
   <si>
-    <t>-270.8602 psi</t>
-  </si>
-  <si>
-    <t>284.4470 K</t>
-  </si>
-  <si>
-    <t>1771.8713 psi</t>
+    <t>-25.3127 psi</t>
+  </si>
+  <si>
+    <t>288.0562 K</t>
+  </si>
+  <si>
+    <t>1831.1912 psi</t>
   </si>
   <si>
     <t>288.7060 K</t>
@@ -87,103 +74,130 @@
     <t>1842.0000 psi</t>
   </si>
   <si>
-    <t>1217.3271 ft/s</t>
-  </si>
-  <si>
-    <t>267.4385 ft/s</t>
+    <t>0.0853</t>
+  </si>
+  <si>
+    <t>1225.0257 ft/s</t>
+  </si>
+  <si>
+    <t>104.4647 ft/s</t>
   </si>
   <si>
     <t>Valve, stations 4-5:</t>
   </si>
   <si>
-    <t>-2.7802 psi</t>
-  </si>
-  <si>
-    <t>282.7370 K</t>
-  </si>
-  <si>
-    <t>1487.7094 psi</t>
-  </si>
-  <si>
-    <t>1571.1398 psi</t>
-  </si>
-  <si>
-    <t>1213.6625 ft/s</t>
-  </si>
-  <si>
-    <t>316.6061 ft/s</t>
+    <t>-2.4149 psi</t>
+  </si>
+  <si>
+    <t>288.0378 K</t>
+  </si>
+  <si>
+    <t>1805.7262 psi</t>
+  </si>
+  <si>
+    <t>1816.6873 psi</t>
+  </si>
+  <si>
+    <t>0.0865</t>
+  </si>
+  <si>
+    <t>1224.9867 ft/s</t>
+  </si>
+  <si>
+    <t>105.9312 ft/s</t>
   </si>
   <si>
     <t>Tube, stations 6-7:</t>
   </si>
   <si>
-    <t>-91.9634 psi</t>
-  </si>
-  <si>
-    <t>282.9322 K</t>
-  </si>
-  <si>
-    <t>1488.2000 psi</t>
-  </si>
-  <si>
-    <t>1200.1078 ft/s</t>
-  </si>
-  <si>
-    <t>314.6876 ft/s</t>
+    <t>-7.6656 psi</t>
+  </si>
+  <si>
+    <t>284.3344 K</t>
+  </si>
+  <si>
+    <t>1745.5513 psi</t>
+  </si>
+  <si>
+    <t>0.2231</t>
+  </si>
+  <si>
+    <t>1215.7790 ft/s</t>
+  </si>
+  <si>
+    <t>271.1796 ft/s</t>
   </si>
   <si>
     <t>Valve, stations 9-10:</t>
   </si>
   <si>
-    <t>-3.0026 psi</t>
-  </si>
-  <si>
-    <t>282.9123 K</t>
-  </si>
-  <si>
-    <t>1485.2605 psi</t>
-  </si>
-  <si>
-    <t>1568.3596 psi</t>
-  </si>
-  <si>
-    <t>1199.9220 ft/s</t>
-  </si>
-  <si>
-    <t>315.2703 ft/s</t>
+    <t>-2.4560 psi</t>
+  </si>
+  <si>
+    <t>284.3234 K</t>
+  </si>
+  <si>
+    <t>1743.0386 psi</t>
+  </si>
+  <si>
+    <t>1814.2724 psi</t>
+  </si>
+  <si>
+    <t>0.2234</t>
+  </si>
+  <si>
+    <t>1215.6308 ft/s</t>
+  </si>
+  <si>
+    <t>271.5426 ft/s</t>
   </si>
   <si>
     <t>Tube, stations 11-12:</t>
   </si>
   <si>
-    <t>-26.4222 psi</t>
+    <t>-2.2754 psi</t>
+  </si>
+  <si>
+    <t>288.0382 K</t>
+  </si>
+  <si>
+    <t>1803.3046 psi</t>
+  </si>
+  <si>
+    <t>0.0866</t>
+  </si>
+  <si>
+    <t>1223.5464 ft/s</t>
+  </si>
+  <si>
+    <t>105.9949 ft/s</t>
   </si>
   <si>
     <t>Regulator, stations 13-14:</t>
   </si>
   <si>
-    <t>-131.0228 psi</t>
-  </si>
-  <si>
-    <t>282.1047 K</t>
-  </si>
-  <si>
-    <t>1387.4778 psi</t>
-  </si>
-  <si>
-    <t>1476.3962 psi</t>
-  </si>
-  <si>
-    <t>1198.2082 ft/s</t>
-  </si>
-  <si>
-    <t>336.5257 ft/s</t>
+    <t>-100.4018 psi</t>
+  </si>
+  <si>
+    <t>288.0325 K</t>
+  </si>
+  <si>
+    <t>1795.5920 psi</t>
+  </si>
+  <si>
+    <t>1806.6068 psi</t>
+  </si>
+  <si>
+    <t>1223.5343 ft/s</t>
+  </si>
+  <si>
+    <t>106.4480 ft/s</t>
   </si>
   <si>
     <t>Tube, stations 15-16:</t>
   </si>
   <si>
-    <t>-60.1815 psi</t>
+    <t>-4.8099 psi</t>
   </si>
   <si>
     <t>2.0000</t>
@@ -192,313 +206,448 @@
     <t>Valve, stations 17-18:</t>
   </si>
   <si>
-    <t>-3.5266 psi</t>
-  </si>
-  <si>
-    <t>287.0408 K</t>
-  </si>
-  <si>
-    <t>1453.4004 psi</t>
-  </si>
-  <si>
-    <t>1203.8673 ft/s</t>
-  </si>
-  <si>
-    <t>169.7603 ft/s</t>
+    <t>-2.6145 psi</t>
+  </si>
+  <si>
+    <t>287.5538 K</t>
+  </si>
+  <si>
+    <t>1787.7737 psi</t>
+  </si>
+  <si>
+    <t>0.1140</t>
+  </si>
+  <si>
+    <t>1222.1188 ft/s</t>
+  </si>
+  <si>
+    <t>139.2704 ft/s</t>
   </si>
   <si>
     <t>Tube, stations 19-20:</t>
   </si>
   <si>
-    <t>-5.1618 psi</t>
-  </si>
-  <si>
-    <t>287.0345 K</t>
-  </si>
-  <si>
-    <t>1450.3507 psi</t>
-  </si>
-  <si>
-    <t>1473.3935 psi</t>
-  </si>
-  <si>
-    <t>1203.6983 ft/s</t>
-  </si>
-  <si>
-    <t>170.1044 ft/s</t>
+    <t>-0.4019 psi</t>
+  </si>
+  <si>
+    <t>287.5509 K</t>
+  </si>
+  <si>
+    <t>1785.2927 psi</t>
+  </si>
+  <si>
+    <t>1804.1508 psi</t>
+  </si>
+  <si>
+    <t>0.1141</t>
+  </si>
+  <si>
+    <t>1221.9851 ft/s</t>
+  </si>
+  <si>
+    <t>139.4536 ft/s</t>
   </si>
   <si>
     <t>Valve, stations 22-23:</t>
   </si>
   <si>
-    <t>-3.0053 psi</t>
+    <t>-2.4575 psi</t>
+  </si>
+  <si>
+    <t>288.5244 K</t>
+  </si>
+  <si>
+    <t>1801.1787 psi</t>
+  </si>
+  <si>
+    <t>0.0452</t>
+  </si>
+  <si>
+    <t>1224.0520 ft/s</t>
+  </si>
+  <si>
+    <t>55.2868 ft/s</t>
   </si>
   <si>
     <t>Tube, stations 24-25:</t>
   </si>
   <si>
-    <t>-61.1431 psi</t>
-  </si>
-  <si>
-    <t>286.9716 K</t>
-  </si>
-  <si>
-    <t>1423.4945 psi</t>
-  </si>
-  <si>
-    <t>1446.9714 psi</t>
-  </si>
-  <si>
-    <t>1203.5664 ft/s</t>
-  </si>
-  <si>
-    <t>173.2757 ft/s</t>
+    <t>-5.2277 psi</t>
+  </si>
+  <si>
+    <t>288.5240 K</t>
+  </si>
+  <si>
+    <t>1798.8995 psi</t>
+  </si>
+  <si>
+    <t>1801.8754 psi</t>
+  </si>
+  <si>
+    <t>1224.0510 ft/s</t>
+  </si>
+  <si>
+    <t>55.3568 ft/s</t>
   </si>
   <si>
     <t>Regulator, stations 26-27:</t>
   </si>
   <si>
-    <t>-135.3502 psi</t>
-  </si>
-  <si>
-    <t>286.9778 K</t>
-  </si>
-  <si>
-    <t>1423.5049 psi</t>
-  </si>
-  <si>
-    <t>1202.2082 ft/s</t>
-  </si>
-  <si>
-    <t>173.1980 ft/s</t>
+    <t>-100.6597 psi</t>
+  </si>
+  <si>
+    <t>287.5483 K</t>
+  </si>
+  <si>
+    <t>1782.9942 psi</t>
+  </si>
+  <si>
+    <t>0.1143</t>
+  </si>
+  <si>
+    <t>1221.8613 ft/s</t>
+  </si>
+  <si>
+    <t>139.6238 ft/s</t>
   </si>
   <si>
     <t>Tube, stations 28-29:</t>
   </si>
   <si>
-    <t>-53.0026 psi</t>
-  </si>
-  <si>
-    <t>286.6447 K</t>
-  </si>
-  <si>
-    <t>1290.1080 psi</t>
-  </si>
-  <si>
-    <t>1315.9486 psi</t>
-  </si>
-  <si>
-    <t>1194.7307 ft/s</t>
-  </si>
-  <si>
-    <t>190.4985 ft/s</t>
+    <t>-4.1469 psi</t>
+  </si>
+  <si>
+    <t>287.4215 K</t>
+  </si>
+  <si>
+    <t>1681.5032 psi</t>
+  </si>
+  <si>
+    <t>1701.4736 psi</t>
+  </si>
+  <si>
+    <t>0.1214</t>
+  </si>
+  <si>
+    <t>1216.3723 ft/s</t>
+  </si>
+  <si>
+    <t>147.6163 ft/s</t>
   </si>
   <si>
     <t>Valve, stations 30-31:</t>
   </si>
   <si>
-    <t>-3.6224 psi</t>
+    <t>-2.6202 psi</t>
+  </si>
+  <si>
+    <t>288.5044 K</t>
+  </si>
+  <si>
+    <t>1698.3295 psi</t>
+  </si>
+  <si>
+    <t>0.0480</t>
+  </si>
+  <si>
+    <t>1218.6616 ft/s</t>
+  </si>
+  <si>
+    <t>58.4810 ft/s</t>
   </si>
   <si>
     <t>Tube, stations 32-33:</t>
   </si>
   <si>
-    <t>-4.5350 psi</t>
-  </si>
-  <si>
-    <t>286.4366 K</t>
-  </si>
-  <si>
-    <t>1228.6358 psi</t>
-  </si>
-  <si>
-    <t>1255.7672 psi</t>
-  </si>
-  <si>
-    <t>1194.2969 ft/s</t>
-  </si>
-  <si>
-    <t>199.8845 ft/s</t>
-  </si>
-  <si>
-    <t>286.4559 K</t>
-  </si>
-  <si>
-    <t>1228.6549 psi</t>
-  </si>
-  <si>
-    <t>1191.2359 ft/s</t>
-  </si>
-  <si>
-    <t>199.7391 ft/s</t>
-  </si>
-  <si>
-    <t>286.4440 K</t>
-  </si>
-  <si>
-    <t>1225.0496 psi</t>
-  </si>
-  <si>
-    <t>1252.2405 psi</t>
-  </si>
-  <si>
-    <t>1191.0297 ft/s</t>
-  </si>
-  <si>
-    <t>200.3101 ft/s</t>
-  </si>
-  <si>
-    <t>286.4246 K</t>
-  </si>
-  <si>
-    <t>1219.7703 psi</t>
-  </si>
-  <si>
-    <t>1247.0788 psi</t>
-  </si>
-  <si>
-    <t>1190.9896 ft/s</t>
-  </si>
-  <si>
-    <t>201.1635 ft/s</t>
+    <t>-0.3465 psi</t>
+  </si>
+  <si>
+    <t>288.5033 K</t>
+  </si>
+  <si>
+    <t>1693.5107 psi</t>
+  </si>
+  <si>
+    <t>1696.6637 psi</t>
+  </si>
+  <si>
+    <t>0.0481</t>
+  </si>
+  <si>
+    <t>1218.6591 ft/s</t>
+  </si>
+  <si>
+    <t>58.6472 ft/s</t>
+  </si>
+  <si>
+    <t>287.4149 K</t>
+  </si>
+  <si>
+    <t>1676.6376 psi</t>
+  </si>
+  <si>
+    <t>0.1217</t>
+  </si>
+  <si>
+    <t>1216.1081 ft/s</t>
+  </si>
+  <si>
+    <t>148.0245 ft/s</t>
+  </si>
+  <si>
+    <t>287.4112 K</t>
+  </si>
+  <si>
+    <t>1673.9927 psi</t>
+  </si>
+  <si>
+    <t>1694.0492 psi</t>
+  </si>
+  <si>
+    <t>0.1219</t>
+  </si>
+  <si>
+    <t>1215.9644 ft/s</t>
+  </si>
+  <si>
+    <t>148.2474 ft/s</t>
+  </si>
+  <si>
+    <t>288.5028 K</t>
+  </si>
+  <si>
+    <t>1690.8919 psi</t>
+  </si>
+  <si>
+    <t>0.0482</t>
+  </si>
+  <si>
+    <t>1218.2713 ft/s</t>
+  </si>
+  <si>
+    <t>58.7276 ft/s</t>
+  </si>
+  <si>
+    <t>288.5027 K</t>
+  </si>
+  <si>
+    <t>1690.4892 psi</t>
+  </si>
+  <si>
+    <t>1693.6472 psi</t>
+  </si>
+  <si>
+    <t>1218.2711 ft/s</t>
+  </si>
+  <si>
+    <t>58.7416 ft/s</t>
   </si>
   <si>
     <t>1.0000</t>
   </si>
   <si>
-    <t>287.2942 K</t>
-  </si>
-  <si>
-    <t>1456.8849 psi</t>
-  </si>
-  <si>
-    <t>1204.3986 ft/s</t>
-  </si>
-  <si>
-    <t>156.3117 ft/s</t>
-  </si>
-  <si>
-    <t>287.2889 K</t>
-  </si>
-  <si>
-    <t>1453.8398 psi</t>
-  </si>
-  <si>
-    <t>1473.3909 psi</t>
-  </si>
-  <si>
-    <t>1204.2314 ft/s</t>
-  </si>
-  <si>
-    <t>156.6278 ft/s</t>
-  </si>
-  <si>
-    <t>287.1611 K</t>
-  </si>
-  <si>
-    <t>1391.8268 psi</t>
-  </si>
-  <si>
-    <t>1412.2478 psi</t>
-  </si>
-  <si>
-    <t>1203.9637 ft/s</t>
-  </si>
-  <si>
-    <t>163.5336 ft/s</t>
-  </si>
-  <si>
-    <t>287.1739 K</t>
-  </si>
-  <si>
-    <t>1391.8472 psi</t>
-  </si>
-  <si>
-    <t>1200.8177 ft/s</t>
-  </si>
-  <si>
-    <t>163.3679 ft/s</t>
-  </si>
-  <si>
-    <t>286.8591 K</t>
-  </si>
-  <si>
-    <t>1254.3041 psi</t>
-  </si>
-  <si>
-    <t>1276.8975 psi</t>
-  </si>
-  <si>
-    <t>1193.1627 ft/s</t>
-  </si>
-  <si>
-    <t>180.7288 ft/s</t>
-  </si>
-  <si>
-    <t>286.6915 K</t>
-  </si>
-  <si>
-    <t>1200.2861 psi</t>
-  </si>
-  <si>
-    <t>1223.8949 psi</t>
-  </si>
-  <si>
-    <t>1192.8141 ft/s</t>
-  </si>
-  <si>
-    <t>188.7520 ft/s</t>
-  </si>
-  <si>
-    <t>286.7068 K</t>
-  </si>
-  <si>
-    <t>1200.2996 psi</t>
-  </si>
-  <si>
-    <t>1190.1184 ft/s</t>
-  </si>
-  <si>
-    <t>188.6398 ft/s</t>
-  </si>
-  <si>
-    <t>286.6957 K</t>
-  </si>
-  <si>
-    <t>1196.6053 psi</t>
-  </si>
-  <si>
-    <t>1220.2725 psi</t>
-  </si>
-  <si>
-    <t>1189.9091 ft/s</t>
-  </si>
-  <si>
-    <t>189.2071 ft/s</t>
-  </si>
-  <si>
-    <t>286.6803 K</t>
-  </si>
-  <si>
-    <t>1191.9786 psi</t>
-  </si>
-  <si>
-    <t>1215.7375 psi</t>
-  </si>
-  <si>
-    <t>1189.8771 ft/s</t>
-  </si>
-  <si>
-    <t>189.9313 ft/s</t>
+    <t>287.7281 K</t>
+  </si>
+  <si>
+    <t>1790.6147 psi</t>
+  </si>
+  <si>
+    <t>0.1050</t>
+  </si>
+  <si>
+    <t>1222.4891 ft/s</t>
+  </si>
+  <si>
+    <t>128.3053 ft/s</t>
+  </si>
+  <si>
+    <t>287.7256 K</t>
+  </si>
+  <si>
+    <t>1788.1361 psi</t>
+  </si>
+  <si>
+    <t>1804.1493 psi</t>
+  </si>
+  <si>
+    <t>0.1051</t>
+  </si>
+  <si>
+    <t>1222.3563 ft/s</t>
+  </si>
+  <si>
+    <t>128.4738 ft/s</t>
+  </si>
+  <si>
+    <t>288.5517 K</t>
+  </si>
+  <si>
+    <t>1801.6224 psi</t>
+  </si>
+  <si>
+    <t>0.0416</t>
+  </si>
+  <si>
+    <t>1224.1096 ft/s</t>
+  </si>
+  <si>
+    <t>50.9762 ft/s</t>
+  </si>
+  <si>
+    <t>288.5508 K</t>
+  </si>
+  <si>
+    <t>1796.3873 psi</t>
+  </si>
+  <si>
+    <t>1798.9216 psi</t>
+  </si>
+  <si>
+    <t>0.0418</t>
+  </si>
+  <si>
+    <t>1224.1077 ft/s</t>
+  </si>
+  <si>
+    <t>51.1246 ft/s</t>
+  </si>
+  <si>
+    <t>287.7205 K</t>
+  </si>
+  <si>
+    <t>1782.8632 psi</t>
+  </si>
+  <si>
+    <t>0.1054</t>
+  </si>
+  <si>
+    <t>1222.0736 ft/s</t>
+  </si>
+  <si>
+    <t>128.8338 ft/s</t>
+  </si>
+  <si>
+    <t>287.6124 K</t>
+  </si>
+  <si>
+    <t>1681.2761 psi</t>
+  </si>
+  <si>
+    <t>1698.2620 psi</t>
+  </si>
+  <si>
+    <t>0.1120</t>
+  </si>
+  <si>
+    <t>1216.6089 ft/s</t>
+  </si>
+  <si>
+    <t>136.2261 ft/s</t>
+  </si>
+  <si>
+    <t>288.5340 K</t>
+  </si>
+  <si>
+    <t>1695.5841 psi</t>
+  </si>
+  <si>
+    <t>0.0443</t>
+  </si>
+  <si>
+    <t>1218.5568 ft/s</t>
+  </si>
+  <si>
+    <t>54.0183 ft/s</t>
+  </si>
+  <si>
+    <t>288.5332 K</t>
+  </si>
+  <si>
+    <t>1691.4306 psi</t>
+  </si>
+  <si>
+    <t>1694.1151 psi</t>
+  </si>
+  <si>
+    <t>0.0444</t>
+  </si>
+  <si>
+    <t>1218.5550 ft/s</t>
+  </si>
+  <si>
+    <t>54.1508 ft/s</t>
+  </si>
+  <si>
+    <t>287.6075 K</t>
+  </si>
+  <si>
+    <t>1677.0885 psi</t>
+  </si>
+  <si>
+    <t>0.1123</t>
+  </si>
+  <si>
+    <t>1216.3829 ft/s</t>
+  </si>
+  <si>
+    <t>136.5506 ft/s</t>
+  </si>
+  <si>
+    <t>287.6044 K</t>
+  </si>
+  <si>
+    <t>1674.4425 psi</t>
+  </si>
+  <si>
+    <t>1691.4949 psi</t>
+  </si>
+  <si>
+    <t>0.1124</t>
+  </si>
+  <si>
+    <t>1216.2400 ft/s</t>
+  </si>
+  <si>
+    <t>136.7565 ft/s</t>
+  </si>
+  <si>
+    <t>288.5328 K</t>
+  </si>
+  <si>
+    <t>1688.8067 psi</t>
+  </si>
+  <si>
+    <t>0.0445</t>
+  </si>
+  <si>
+    <t>1218.2014 ft/s</t>
+  </si>
+  <si>
+    <t>54.2262 ft/s</t>
+  </si>
+  <si>
+    <t>288.5327 K</t>
+  </si>
+  <si>
+    <t>1688.4597 psi</t>
+  </si>
+  <si>
+    <t>1691.1484 psi</t>
+  </si>
+  <si>
+    <t>1218.2013 ft/s</t>
+  </si>
+  <si>
+    <t>54.2374 ft/s</t>
+  </si>
+  <si>
+    <t>x</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="167" formatCode="0.00000"/>
-  </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -548,13 +697,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -570,55 +717,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>21</xdr:col>
-      <xdr:colOff>85725</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>285863</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>86771</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4F1258EE-DA75-8180-C829-DD8F7C8F68D5}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13830300" y="1543050"/>
-          <a:ext cx="809738" cy="7497221"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -907,7 +1005,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -915,21 +1013,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:L37"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:L34"/>
+  <sheetFormatPr defaultRowHeight="14.35" x14ac:dyDescent="0.5"/>
   <cols>
-    <col min="2" max="2" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="7.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="23.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.28515625" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="30.29296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.5">
       <c r="B1" s="1" t="s">
         <v>0</v>
       </c>
@@ -962,7 +1052,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -976,7 +1066,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -992,880 +1082,871 @@
       <c r="E3" t="s">
         <v>16</v>
       </c>
-      <c r="F3" s="3">
-        <v>0.21970000000000001</v>
+      <c r="F3" t="s">
+        <v>17</v>
       </c>
       <c r="G3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="K3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D4" t="s">
         <v>15</v>
       </c>
       <c r="E4" t="s">
-        <v>23</v>
-      </c>
-      <c r="F4" s="3">
-        <v>0.26090000000000002</v>
+        <v>24</v>
+      </c>
+      <c r="F4" t="s">
+        <v>25</v>
       </c>
       <c r="G4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="H4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="K4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="L4" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5" t="s">
         <v>15</v>
       </c>
       <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" s="3">
-        <v>0.26219999999999999</v>
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>32</v>
       </c>
       <c r="G5" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="K5" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="L5" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="D6" t="s">
         <v>15</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
-      </c>
-      <c r="F6" s="3">
-        <v>0.26269999999999999</v>
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>40</v>
       </c>
       <c r="G6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="H6" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="K6" t="s">
-        <v>39</v>
+        <v>43</v>
       </c>
       <c r="L6" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="C7" t="s">
-        <v>35</v>
+        <v>46</v>
       </c>
       <c r="D7" t="s">
         <v>15</v>
       </c>
       <c r="E7" t="s">
-        <v>36</v>
-      </c>
-      <c r="F7" s="3">
-        <v>0.26269999999999999</v>
+        <v>39</v>
+      </c>
+      <c r="F7" t="s">
+        <v>47</v>
       </c>
       <c r="G7" t="s">
-        <v>37</v>
+        <v>48</v>
       </c>
       <c r="H7" t="s">
-        <v>38</v>
+        <v>49</v>
       </c>
       <c r="K7" t="s">
-        <v>41</v>
+        <v>50</v>
       </c>
       <c r="L7" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>43</v>
+        <v>52</v>
       </c>
       <c r="C8" t="s">
-        <v>44</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
         <v>15</v>
       </c>
       <c r="E8" t="s">
-        <v>45</v>
-      </c>
-      <c r="F8" s="3">
-        <v>0.28089999999999998</v>
+        <v>54</v>
+      </c>
+      <c r="F8" t="s">
+        <v>206</v>
       </c>
       <c r="G8" t="s">
-        <v>46</v>
+        <v>55</v>
       </c>
       <c r="H8" t="s">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="K8" t="s">
-        <v>48</v>
+        <v>57</v>
       </c>
       <c r="L8" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>50</v>
-      </c>
-      <c r="F9" s="3"/>
+        <v>59</v>
+      </c>
       <c r="K9" t="s">
-        <v>51</v>
+        <v>60</v>
       </c>
       <c r="L9" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A10" s="1">
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>53</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
+        <v>63</v>
+      </c>
+      <c r="D10" t="s">
+        <v>15</v>
+      </c>
+      <c r="E10" t="s">
         <v>54</v>
       </c>
-      <c r="D10" t="s">
-        <v>15</v>
-      </c>
-      <c r="E10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F10" s="3">
-        <v>0.14099999999999999</v>
+      <c r="F10" t="s">
+        <v>64</v>
       </c>
       <c r="G10" t="s">
-        <v>55</v>
+        <v>65</v>
       </c>
       <c r="H10" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="K10" t="s">
-        <v>57</v>
+        <v>67</v>
       </c>
       <c r="L10" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>59</v>
+        <v>69</v>
       </c>
       <c r="C11" t="s">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="D11" t="s">
         <v>15</v>
       </c>
       <c r="E11" t="s">
-        <v>61</v>
-      </c>
-      <c r="F11" s="3">
-        <v>0.14130000000000001</v>
+        <v>71</v>
+      </c>
+      <c r="F11" t="s">
+        <v>72</v>
       </c>
       <c r="G11" t="s">
-        <v>62</v>
+        <v>73</v>
       </c>
       <c r="H11" t="s">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="K11" t="s">
-        <v>64</v>
+        <v>75</v>
       </c>
       <c r="L11" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+        <v>76</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>59</v>
+        <v>77</v>
       </c>
       <c r="C12" t="s">
-        <v>60</v>
+        <v>78</v>
       </c>
       <c r="D12" t="s">
         <v>15</v>
       </c>
       <c r="E12" t="s">
-        <v>61</v>
-      </c>
-      <c r="F12" s="3">
-        <v>0.14130000000000001</v>
+        <v>71</v>
+      </c>
+      <c r="F12" t="s">
+        <v>79</v>
       </c>
       <c r="G12" t="s">
-        <v>62</v>
+        <v>80</v>
       </c>
       <c r="H12" t="s">
-        <v>63</v>
+        <v>81</v>
       </c>
       <c r="K12" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="L12" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>68</v>
+        <v>84</v>
       </c>
       <c r="C13" t="s">
-        <v>69</v>
+        <v>85</v>
       </c>
       <c r="D13" t="s">
         <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
-      </c>
-      <c r="F13" s="3">
-        <v>0.14399999999999999</v>
+        <v>86</v>
+      </c>
+      <c r="F13" t="s">
+        <v>79</v>
       </c>
       <c r="G13" t="s">
-        <v>71</v>
+        <v>87</v>
       </c>
       <c r="H13" t="s">
-        <v>72</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s">
-        <v>73</v>
+        <v>89</v>
       </c>
       <c r="L13" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A14" s="1">
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>75</v>
+        <v>91</v>
       </c>
       <c r="C14" t="s">
-        <v>76</v>
+        <v>92</v>
       </c>
       <c r="D14" t="s">
         <v>15</v>
       </c>
       <c r="E14" t="s">
-        <v>70</v>
-      </c>
-      <c r="F14" s="3">
-        <v>0.14410000000000001</v>
+        <v>86</v>
+      </c>
+      <c r="F14" t="s">
+        <v>93</v>
       </c>
       <c r="G14" t="s">
-        <v>77</v>
+        <v>94</v>
       </c>
       <c r="H14" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="K14" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="L14" t="s">
-        <v>80</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A15" s="1">
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="C15" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
       <c r="D15" t="s">
         <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>83</v>
-      </c>
-      <c r="F15" s="3">
-        <v>0.15939999999999999</v>
+        <v>100</v>
+      </c>
+      <c r="F15" t="s">
+        <v>101</v>
       </c>
       <c r="G15" t="s">
-        <v>84</v>
+        <v>102</v>
       </c>
       <c r="H15" t="s">
-        <v>85</v>
+        <v>103</v>
       </c>
       <c r="K15" t="s">
-        <v>86</v>
+        <v>104</v>
       </c>
       <c r="L15" t="s">
-        <v>87</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.5">
       <c r="A16" s="1">
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>81</v>
+        <v>106</v>
       </c>
       <c r="C16" t="s">
-        <v>82</v>
+        <v>107</v>
       </c>
       <c r="D16" t="s">
         <v>15</v>
       </c>
       <c r="E16" t="s">
-        <v>83</v>
-      </c>
-      <c r="F16" s="3">
-        <v>0.15939999999999999</v>
+        <v>100</v>
+      </c>
+      <c r="F16" t="s">
+        <v>108</v>
       </c>
       <c r="G16" t="s">
-        <v>84</v>
+        <v>109</v>
       </c>
       <c r="H16" t="s">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="K16" t="s">
-        <v>88</v>
+        <v>111</v>
       </c>
       <c r="L16" t="s">
-        <v>89</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A17" s="1">
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>90</v>
+        <v>113</v>
       </c>
       <c r="C17" t="s">
-        <v>91</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
         <v>15</v>
       </c>
       <c r="E17" t="s">
-        <v>92</v>
-      </c>
-      <c r="F17" s="3">
-        <v>0.16739999999999999</v>
+        <v>115</v>
+      </c>
+      <c r="F17" t="s">
+        <v>116</v>
       </c>
       <c r="G17" t="s">
-        <v>93</v>
+        <v>117</v>
       </c>
       <c r="H17" t="s">
-        <v>94</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A18" s="1">
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>95</v>
+        <v>119</v>
       </c>
       <c r="C18" t="s">
-        <v>96</v>
+        <v>120</v>
       </c>
       <c r="D18" t="s">
         <v>15</v>
       </c>
       <c r="E18" t="s">
-        <v>92</v>
-      </c>
-      <c r="F18" s="3">
-        <v>0.16769999999999999</v>
+        <v>115</v>
+      </c>
+      <c r="F18" t="s">
+        <v>121</v>
       </c>
       <c r="G18" t="s">
-        <v>97</v>
+        <v>122</v>
       </c>
       <c r="H18" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A19" s="1">
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>99</v>
+        <v>124</v>
       </c>
       <c r="C19" t="s">
-        <v>100</v>
+        <v>125</v>
       </c>
       <c r="D19" t="s">
         <v>15</v>
       </c>
       <c r="E19" t="s">
-        <v>101</v>
-      </c>
-      <c r="F19" s="3">
-        <v>0.16819999999999999</v>
+        <v>126</v>
+      </c>
+      <c r="F19" t="s">
+        <v>127</v>
       </c>
       <c r="G19" t="s">
-        <v>102</v>
+        <v>128</v>
       </c>
       <c r="H19" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A20" s="1">
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>99</v>
+        <v>130</v>
       </c>
       <c r="C20" t="s">
-        <v>100</v>
+        <v>131</v>
       </c>
       <c r="D20" t="s">
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>101</v>
-      </c>
-      <c r="F20" s="3">
-        <v>0.16819999999999999</v>
+        <v>126</v>
+      </c>
+      <c r="F20" t="s">
+        <v>132</v>
       </c>
       <c r="G20" t="s">
-        <v>102</v>
+        <v>133</v>
       </c>
       <c r="H20" t="s">
-        <v>103</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A21" s="1">
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>104</v>
+        <v>135</v>
       </c>
       <c r="C21" t="s">
-        <v>105</v>
+        <v>136</v>
       </c>
       <c r="D21" t="s">
         <v>15</v>
       </c>
       <c r="E21" t="s">
-        <v>106</v>
-      </c>
-      <c r="F21" s="3">
-        <v>0.16889999999999999</v>
+        <v>137</v>
+      </c>
+      <c r="F21" t="s">
+        <v>132</v>
       </c>
       <c r="G21" t="s">
-        <v>107</v>
+        <v>138</v>
       </c>
       <c r="H21" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A22" s="1">
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>109</v>
-      </c>
-      <c r="F22" s="3"/>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A23" s="1">
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="C23" t="s">
-        <v>111</v>
+        <v>142</v>
       </c>
       <c r="D23" t="s">
         <v>15</v>
       </c>
       <c r="E23" t="s">
-        <v>45</v>
-      </c>
-      <c r="F23" s="3">
-        <v>0.1298</v>
+        <v>54</v>
+      </c>
+      <c r="F23" t="s">
+        <v>143</v>
       </c>
       <c r="G23" t="s">
-        <v>112</v>
+        <v>144</v>
       </c>
       <c r="H23" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A24" s="1">
         <v>23</v>
       </c>
       <c r="B24" t="s">
-        <v>114</v>
+        <v>146</v>
       </c>
       <c r="C24" t="s">
-        <v>115</v>
+        <v>147</v>
       </c>
       <c r="D24" t="s">
         <v>15</v>
       </c>
       <c r="E24" t="s">
-        <v>116</v>
-      </c>
-      <c r="F24" s="3">
-        <v>0.13009999999999999</v>
+        <v>148</v>
+      </c>
+      <c r="F24" t="s">
+        <v>149</v>
       </c>
       <c r="G24" t="s">
-        <v>117</v>
+        <v>150</v>
       </c>
       <c r="H24" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A25" s="1">
         <v>24</v>
       </c>
       <c r="B25" t="s">
-        <v>114</v>
+        <v>152</v>
       </c>
       <c r="C25" t="s">
-        <v>115</v>
+        <v>153</v>
       </c>
       <c r="D25" t="s">
         <v>15</v>
       </c>
       <c r="E25" t="s">
-        <v>116</v>
-      </c>
-      <c r="F25" s="3">
-        <v>0.13009999999999999</v>
+        <v>148</v>
+      </c>
+      <c r="F25" t="s">
+        <v>154</v>
       </c>
       <c r="G25" t="s">
-        <v>117</v>
+        <v>155</v>
       </c>
       <c r="H25" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A26" s="1">
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>119</v>
+        <v>157</v>
       </c>
       <c r="C26" t="s">
-        <v>120</v>
+        <v>158</v>
       </c>
       <c r="D26" t="s">
         <v>15</v>
       </c>
       <c r="E26" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" s="3">
-        <v>0.1358</v>
+        <v>159</v>
+      </c>
+      <c r="F26" t="s">
+        <v>160</v>
       </c>
       <c r="G26" t="s">
-        <v>122</v>
+        <v>161</v>
       </c>
       <c r="H26" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A27" s="1">
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>163</v>
       </c>
       <c r="C27" t="s">
-        <v>125</v>
+        <v>164</v>
       </c>
       <c r="D27" t="s">
         <v>15</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
-      </c>
-      <c r="F27" s="3">
-        <v>0.13600000000000001</v>
+        <v>159</v>
+      </c>
+      <c r="F27" t="s">
+        <v>165</v>
       </c>
       <c r="G27" t="s">
-        <v>126</v>
+        <v>166</v>
       </c>
       <c r="H27" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A28" s="1">
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>128</v>
+        <v>168</v>
       </c>
       <c r="C28" t="s">
-        <v>129</v>
+        <v>169</v>
       </c>
       <c r="D28" t="s">
         <v>15</v>
       </c>
       <c r="E28" t="s">
-        <v>130</v>
-      </c>
-      <c r="F28" s="3">
-        <v>0.1515</v>
+        <v>170</v>
+      </c>
+      <c r="F28" t="s">
+        <v>171</v>
       </c>
       <c r="G28" t="s">
-        <v>131</v>
+        <v>172</v>
       </c>
       <c r="H28" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A29" s="1">
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>128</v>
+        <v>174</v>
       </c>
       <c r="C29" t="s">
-        <v>129</v>
+        <v>175</v>
       </c>
       <c r="D29" t="s">
         <v>15</v>
       </c>
       <c r="E29" t="s">
-        <v>130</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0.1515</v>
+        <v>170</v>
+      </c>
+      <c r="F29" t="s">
+        <v>176</v>
       </c>
       <c r="G29" t="s">
-        <v>131</v>
+        <v>177</v>
       </c>
       <c r="H29" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A30" s="1">
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>133</v>
+        <v>179</v>
       </c>
       <c r="C30" t="s">
-        <v>134</v>
+        <v>180</v>
       </c>
       <c r="D30" t="s">
         <v>15</v>
       </c>
       <c r="E30" t="s">
-        <v>135</v>
-      </c>
-      <c r="F30" s="3">
-        <v>0.15820000000000001</v>
+        <v>181</v>
+      </c>
+      <c r="F30" t="s">
+        <v>182</v>
       </c>
       <c r="G30" t="s">
-        <v>136</v>
+        <v>183</v>
       </c>
       <c r="H30" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A31" s="1">
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>138</v>
+        <v>185</v>
       </c>
       <c r="C31" t="s">
-        <v>139</v>
+        <v>186</v>
       </c>
       <c r="D31" t="s">
         <v>15</v>
       </c>
       <c r="E31" t="s">
-        <v>135</v>
-      </c>
-      <c r="F31" s="3">
-        <v>0.1585</v>
+        <v>181</v>
+      </c>
+      <c r="F31" t="s">
+        <v>187</v>
       </c>
       <c r="G31" t="s">
-        <v>140</v>
+        <v>188</v>
       </c>
       <c r="H31" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A32" s="1">
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>190</v>
       </c>
       <c r="C32" t="s">
-        <v>143</v>
+        <v>191</v>
       </c>
       <c r="D32" t="s">
         <v>15</v>
       </c>
       <c r="E32" t="s">
-        <v>144</v>
-      </c>
-      <c r="F32" s="3">
-        <v>0.159</v>
+        <v>192</v>
+      </c>
+      <c r="F32" t="s">
+        <v>193</v>
       </c>
       <c r="G32" t="s">
-        <v>145</v>
+        <v>194</v>
       </c>
       <c r="H32" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A33" s="1">
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>142</v>
+        <v>196</v>
       </c>
       <c r="C33" t="s">
-        <v>143</v>
+        <v>197</v>
       </c>
       <c r="D33" t="s">
         <v>15</v>
       </c>
       <c r="E33" t="s">
-        <v>144</v>
-      </c>
-      <c r="F33" s="3">
-        <v>0.159</v>
+        <v>192</v>
+      </c>
+      <c r="F33" t="s">
+        <v>198</v>
       </c>
       <c r="G33" t="s">
-        <v>145</v>
+        <v>199</v>
       </c>
       <c r="H33" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.5">
       <c r="A34" s="1">
         <v>33</v>
       </c>
       <c r="B34" t="s">
-        <v>147</v>
+        <v>201</v>
       </c>
       <c r="C34" t="s">
-        <v>148</v>
+        <v>202</v>
       </c>
       <c r="D34" t="s">
         <v>15</v>
       </c>
       <c r="E34" t="s">
-        <v>149</v>
-      </c>
-      <c r="F34" s="3">
-        <v>0.15959999999999999</v>
+        <v>203</v>
+      </c>
+      <c r="F34" t="s">
+        <v>198</v>
       </c>
       <c r="G34" t="s">
-        <v>150</v>
+        <v>204</v>
       </c>
       <c r="H34" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="F37" s="2">
-        <f>MAX(F3:F34)</f>
-        <v>0.28089999999999998</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing r:id="rId1"/>
 </worksheet>
 </file>